--- a/outputs/019f85a1-d7dc-78f2-a59c-972a57621ee3/Daily_Log_Collaboration_Integration_Test.xlsx
+++ b/outputs/019f85a1-d7dc-78f2-a59c-972a57621ee3/Daily_Log_Collaboration_Integration_Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Semester_9_SU26\SEP490\Project\SEP490_G38\outputs\019f85a1-d7dc-78f2-a59c-972a57621ee3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F87B9B-B777-4999-81D4-7B378D60B2F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561FE51E-88F9-4B6E-91BA-A71D525D5250}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7453,7 +7453,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.74791666666666667" right="0.25" top="0.75" bottom="0.98402777777777772" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LFacilitate_Test Case\Company&amp;Rv1.0</oddHeader>
     <oddFooter>&amp;L 02ae-BM/PM/HDCV/FSOFT v2/0&amp;CInternal use&amp;R&amp;P/</oddFooter>
